--- a/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -344,7 +344,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-difficulte-cisis|20260716085853</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-difficulte-cisis|20260916095456</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-procedure-difficulty-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
